--- a/test-data/testData.xlsx
+++ b/test-data/testData.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\WorkSpace\ecommerce_shopfy\test-data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D62F2F21-9FC9-4D4A-9B81-E04D8C5086BE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8B23AA8B-7D1A-4FB7-8E10-9950C735E417}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="29">
   <si>
     <t>Name</t>
   </si>
@@ -48,9 +48,6 @@
     <t>prasad15</t>
   </si>
   <si>
-    <t>testuser15@yopmail.com</t>
-  </si>
-  <si>
     <t>Gender</t>
   </si>
   <si>
@@ -109,6 +106,12 @@
   </si>
   <si>
     <t>Andhra</t>
+  </si>
+  <si>
+    <t>prasad20</t>
+  </si>
+  <si>
+    <t>testuser20@yopmail.com</t>
   </si>
 </sst>
 </file>
@@ -471,43 +474,43 @@
         <v>1</v>
       </c>
       <c r="E1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G1" t="s">
+        <v>11</v>
+      </c>
+      <c r="H1" t="s">
         <v>12</v>
       </c>
-      <c r="H1" t="s">
+      <c r="I1" t="s">
         <v>13</v>
       </c>
-      <c r="I1" t="s">
-        <v>14</v>
-      </c>
       <c r="J1" t="s">
+        <v>15</v>
+      </c>
+      <c r="K1" t="s">
         <v>16</v>
       </c>
-      <c r="K1" t="s">
+      <c r="L1" t="s">
         <v>17</v>
       </c>
-      <c r="L1" t="s">
+      <c r="M1" t="s">
         <v>18</v>
       </c>
-      <c r="M1" t="s">
+      <c r="N1" t="s">
         <v>19</v>
       </c>
-      <c r="N1" t="s">
+      <c r="O1" t="s">
         <v>20</v>
       </c>
-      <c r="O1" t="s">
+      <c r="P1" t="s">
         <v>21</v>
       </c>
-      <c r="P1" t="s">
+      <c r="Q1" t="s">
         <v>22</v>
-      </c>
-      <c r="Q1" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="2" spans="1:17" x14ac:dyDescent="0.3">
@@ -518,22 +521,22 @@
         <v>5</v>
       </c>
       <c r="C2" t="s">
-        <v>6</v>
+        <v>27</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>7</v>
+        <v>28</v>
       </c>
       <c r="E2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G2">
         <v>23</v>
       </c>
       <c r="H2" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I2">
         <v>2000</v>
@@ -545,16 +548,16 @@
         <v>6</v>
       </c>
       <c r="L2" t="s">
+        <v>23</v>
+      </c>
+      <c r="M2" t="s">
         <v>24</v>
       </c>
-      <c r="M2" t="s">
+      <c r="N2" t="s">
+        <v>26</v>
+      </c>
+      <c r="O2" t="s">
         <v>25</v>
-      </c>
-      <c r="N2" t="s">
-        <v>27</v>
-      </c>
-      <c r="O2" t="s">
-        <v>26</v>
       </c>
       <c r="P2">
         <v>500335</v>

--- a/test-data/testData.xlsx
+++ b/test-data/testData.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\WorkSpace\ecommerce_shopfy\test-data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8B23AA8B-7D1A-4FB7-8E10-9950C735E417}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C788A72E-5A68-45A6-ADFF-12E1E360CE49}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -108,10 +108,10 @@
     <t>Andhra</t>
   </si>
   <si>
-    <t>prasad20</t>
-  </si>
-  <si>
-    <t>testuser20@yopmail.com</t>
+    <t>prasad153</t>
+  </si>
+  <si>
+    <t>testuser153@yopmail.com</t>
   </si>
 </sst>
 </file>

--- a/test-data/testData.xlsx
+++ b/test-data/testData.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\WorkSpace\ecommerce_shopfy\test-data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C788A72E-5A68-45A6-ADFF-12E1E360CE49}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6BC5F383-4DDB-4B9D-B1C9-08FC82CBB24B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -108,10 +108,10 @@
     <t>Andhra</t>
   </si>
   <si>
-    <t>prasad153</t>
-  </si>
-  <si>
-    <t>testuser153@yopmail.com</t>
+    <t>prasad246</t>
+  </si>
+  <si>
+    <t>testuser246@yopmail.com</t>
   </si>
 </sst>
 </file>

--- a/test-data/testData.xlsx
+++ b/test-data/testData.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\WorkSpace\ecommerce_shopfy\test-data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6BC5F383-4DDB-4B9D-B1C9-08FC82CBB24B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{889864BF-AAA0-4045-A244-6C20433F1F4A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -108,10 +108,10 @@
     <t>Andhra</t>
   </si>
   <si>
-    <t>prasad246</t>
-  </si>
-  <si>
-    <t>testuser246@yopmail.com</t>
+    <t>prasad2300</t>
+  </si>
+  <si>
+    <t>testuser2300@yopmail.com</t>
   </si>
 </sst>
 </file>

--- a/test-data/testData.xlsx
+++ b/test-data/testData.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\WorkSpace\ecommerce_shopfy\test-data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{889864BF-AAA0-4045-A244-6C20433F1F4A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FC4822F5-FF7F-4291-A083-F6FFFED133D6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="31">
   <si>
     <t>Name</t>
   </si>
@@ -108,10 +108,16 @@
     <t>Andhra</t>
   </si>
   <si>
-    <t>prasad2300</t>
-  </si>
-  <si>
-    <t>testuser2300@yopmail.com</t>
+    <t>prasad2301</t>
+  </si>
+  <si>
+    <t>testuser2301@yopmail.com</t>
+  </si>
+  <si>
+    <t>prasad2302</t>
+  </si>
+  <si>
+    <t>testuser2302@yopmail.com</t>
   </si>
 </sst>
 </file>
@@ -440,7 +446,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:Q2"/>
+  <dimension ref="A1:Q3"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="4.88671875" bestFit="1" customWidth="1"/>
@@ -566,10 +572,65 @@
         <v>9977551133</v>
       </c>
     </row>
+    <row r="3" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="E3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G3">
+        <v>23</v>
+      </c>
+      <c r="H3" t="s">
+        <v>14</v>
+      </c>
+      <c r="I3">
+        <v>2000</v>
+      </c>
+      <c r="J3" t="s">
+        <v>6</v>
+      </c>
+      <c r="K3" t="s">
+        <v>6</v>
+      </c>
+      <c r="L3" t="s">
+        <v>23</v>
+      </c>
+      <c r="M3" t="s">
+        <v>24</v>
+      </c>
+      <c r="N3" t="s">
+        <v>26</v>
+      </c>
+      <c r="O3" t="s">
+        <v>25</v>
+      </c>
+      <c r="P3">
+        <v>500335</v>
+      </c>
+      <c r="Q3">
+        <v>9977551133</v>
+      </c>
+    </row>
   </sheetData>
   <hyperlinks>
     <hyperlink ref="D2" r:id="rId1" xr:uid="{D6A3B950-DB4D-483C-A98B-15EE16C9FA39}"/>
     <hyperlink ref="F2" r:id="rId2" xr:uid="{851D07DC-EC92-4332-AB7B-07EC8056F930}"/>
+    <hyperlink ref="D3" r:id="rId3" xr:uid="{BFA3F428-875C-4173-9256-E8078640EBB6}"/>
+    <hyperlink ref="F3" r:id="rId4" xr:uid="{FCC9134B-D3CF-479C-BFA3-459C9941FAC6}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/test-data/testData.xlsx
+++ b/test-data/testData.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\WorkSpace\ecommerce_shopfy\test-data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FC4822F5-FF7F-4291-A083-F6FFFED133D6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B8F800DC-8146-44F2-BA6C-056CB5D5D025}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -108,16 +108,16 @@
     <t>Andhra</t>
   </si>
   <si>
-    <t>prasad2301</t>
-  </si>
-  <si>
-    <t>testuser2301@yopmail.com</t>
-  </si>
-  <si>
-    <t>prasad2302</t>
-  </si>
-  <si>
-    <t>testuser2302@yopmail.com</t>
+    <t>prasad2303</t>
+  </si>
+  <si>
+    <t>prasad2304</t>
+  </si>
+  <si>
+    <t>testuser2303@yopmail.com</t>
+  </si>
+  <si>
+    <t>testuser2304@yopmail.com</t>
   </si>
 </sst>
 </file>
@@ -530,7 +530,7 @@
         <v>27</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -580,7 +580,7 @@
         <v>5</v>
       </c>
       <c r="C3" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D3" s="1" t="s">
         <v>30</v>

--- a/test-data/testData.xlsx
+++ b/test-data/testData.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\WorkSpace\ecommerce_shopfy\test-data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B8F800DC-8146-44F2-BA6C-056CB5D5D025}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E36ECE4E-5244-49D2-8CF4-236A54928204}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -108,16 +108,16 @@
     <t>Andhra</t>
   </si>
   <si>
-    <t>prasad2303</t>
-  </si>
-  <si>
-    <t>prasad2304</t>
-  </si>
-  <si>
-    <t>testuser2303@yopmail.com</t>
-  </si>
-  <si>
-    <t>testuser2304@yopmail.com</t>
+    <t>gvvtest7562</t>
+  </si>
+  <si>
+    <t>gvvtest7562@yopmail.com</t>
+  </si>
+  <si>
+    <t>gvvtest7346</t>
+  </si>
+  <si>
+    <t>gvvtest7346@yopmail.com</t>
   </si>
 </sst>
 </file>
@@ -530,7 +530,7 @@
         <v>27</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -580,7 +580,7 @@
         <v>5</v>
       </c>
       <c r="C3" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D3" s="1" t="s">
         <v>30</v>

--- a/test-data/testData.xlsx
+++ b/test-data/testData.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\WorkSpace\ecommerce_shopfy\test-data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E36ECE4E-5244-49D2-8CF4-236A54928204}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3F74B747-6E97-4796-BFF2-BABA4A7C0194}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="29">
   <si>
     <t>Name</t>
   </si>
@@ -108,16 +108,10 @@
     <t>Andhra</t>
   </si>
   <si>
-    <t>gvvtest7562</t>
-  </si>
-  <si>
-    <t>gvvtest7562@yopmail.com</t>
-  </si>
-  <si>
-    <t>gvvtest7346</t>
-  </si>
-  <si>
-    <t>gvvtest7346@yopmail.com</t>
+    <t>gvvtest7002</t>
+  </si>
+  <si>
+    <t>gvvtest7062@yopmail.com</t>
   </si>
 </sst>
 </file>
@@ -446,7 +440,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:Q3"/>
+  <dimension ref="A1:Q2"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="4.88671875" bestFit="1" customWidth="1"/>
@@ -572,65 +566,10 @@
         <v>9977551133</v>
       </c>
     </row>
-    <row r="3" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
-        <v>3</v>
-      </c>
-      <c r="B3" t="s">
-        <v>5</v>
-      </c>
-      <c r="C3" t="s">
-        <v>29</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="E3" t="s">
-        <v>8</v>
-      </c>
-      <c r="F3" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="G3">
-        <v>23</v>
-      </c>
-      <c r="H3" t="s">
-        <v>14</v>
-      </c>
-      <c r="I3">
-        <v>2000</v>
-      </c>
-      <c r="J3" t="s">
-        <v>6</v>
-      </c>
-      <c r="K3" t="s">
-        <v>6</v>
-      </c>
-      <c r="L3" t="s">
-        <v>23</v>
-      </c>
-      <c r="M3" t="s">
-        <v>24</v>
-      </c>
-      <c r="N3" t="s">
-        <v>26</v>
-      </c>
-      <c r="O3" t="s">
-        <v>25</v>
-      </c>
-      <c r="P3">
-        <v>500335</v>
-      </c>
-      <c r="Q3">
-        <v>9977551133</v>
-      </c>
-    </row>
   </sheetData>
   <hyperlinks>
     <hyperlink ref="D2" r:id="rId1" xr:uid="{D6A3B950-DB4D-483C-A98B-15EE16C9FA39}"/>
     <hyperlink ref="F2" r:id="rId2" xr:uid="{851D07DC-EC92-4332-AB7B-07EC8056F930}"/>
-    <hyperlink ref="D3" r:id="rId3" xr:uid="{BFA3F428-875C-4173-9256-E8078640EBB6}"/>
-    <hyperlink ref="F3" r:id="rId4" xr:uid="{FCC9134B-D3CF-479C-BFA3-459C9941FAC6}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/test-data/testData.xlsx
+++ b/test-data/testData.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\WorkSpace\ecommerce_shopfy\test-data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3F74B747-6E97-4796-BFF2-BABA4A7C0194}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3FD79D87-0F9C-4C05-87CF-A7E30FBFCD35}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="31">
   <si>
     <t>Name</t>
   </si>
@@ -108,10 +108,16 @@
     <t>Andhra</t>
   </si>
   <si>
-    <t>gvvtest7002</t>
-  </si>
-  <si>
-    <t>gvvtest7062@yopmail.com</t>
+    <t>gvvtest79902</t>
+  </si>
+  <si>
+    <t>gvvtest7802@yopmail.com</t>
+  </si>
+  <si>
+    <t>gvvtest76992@yopmail.com</t>
+  </si>
+  <si>
+    <t>gvvtest74170</t>
   </si>
 </sst>
 </file>
@@ -440,7 +446,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:Q2"/>
+  <dimension ref="A1:Q3"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="4.88671875" bestFit="1" customWidth="1"/>
@@ -566,10 +572,65 @@
         <v>9977551133</v>
       </c>
     </row>
+    <row r="3" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C3" t="s">
+        <v>30</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="E3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G3">
+        <v>23</v>
+      </c>
+      <c r="H3" t="s">
+        <v>14</v>
+      </c>
+      <c r="I3">
+        <v>2000</v>
+      </c>
+      <c r="J3" t="s">
+        <v>6</v>
+      </c>
+      <c r="K3" t="s">
+        <v>6</v>
+      </c>
+      <c r="L3" t="s">
+        <v>23</v>
+      </c>
+      <c r="M3" t="s">
+        <v>24</v>
+      </c>
+      <c r="N3" t="s">
+        <v>26</v>
+      </c>
+      <c r="O3" t="s">
+        <v>25</v>
+      </c>
+      <c r="P3">
+        <v>500335</v>
+      </c>
+      <c r="Q3">
+        <v>9977551133</v>
+      </c>
+    </row>
   </sheetData>
   <hyperlinks>
     <hyperlink ref="D2" r:id="rId1" xr:uid="{D6A3B950-DB4D-483C-A98B-15EE16C9FA39}"/>
     <hyperlink ref="F2" r:id="rId2" xr:uid="{851D07DC-EC92-4332-AB7B-07EC8056F930}"/>
+    <hyperlink ref="D3" r:id="rId3" xr:uid="{4D2B3D44-0F7E-46B5-ACE0-D722AEA02DBB}"/>
+    <hyperlink ref="F3" r:id="rId4" xr:uid="{029352C1-01BF-48E4-9A4A-2400EDF19CB2}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/test-data/testData.xlsx
+++ b/test-data/testData.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\WorkSpace\ecommerce_shopfy\test-data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3FD79D87-0F9C-4C05-87CF-A7E30FBFCD35}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{61F5D4E7-47DA-4811-A9D4-401C84CAB400}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -108,16 +108,16 @@
     <t>Andhra</t>
   </si>
   <si>
-    <t>gvvtest79902</t>
-  </si>
-  <si>
-    <t>gvvtest7802@yopmail.com</t>
-  </si>
-  <si>
-    <t>gvvtest76992@yopmail.com</t>
-  </si>
-  <si>
-    <t>gvvtest74170</t>
+    <t>gvvtest71992</t>
+  </si>
+  <si>
+    <t>gvvtest5670@yopmail.com</t>
+  </si>
+  <si>
+    <t>gvvtest10992@yopmail.com</t>
+  </si>
+  <si>
+    <t>gvvtest74040</t>
   </si>
 </sst>
 </file>

--- a/test-data/testData.xlsx
+++ b/test-data/testData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\WorkSpace\ecommerce_shopfy\test-data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{61F5D4E7-47DA-4811-A9D4-401C84CAB400}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3B713BEE-6275-4D82-83B3-B93ABA4FCDE1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1152" yWindow="1152" windowWidth="17280" windowHeight="8880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="29">
   <si>
     <t>Name</t>
   </si>
@@ -108,16 +108,10 @@
     <t>Andhra</t>
   </si>
   <si>
-    <t>gvvtest71992</t>
-  </si>
-  <si>
-    <t>gvvtest5670@yopmail.com</t>
-  </si>
-  <si>
-    <t>gvvtest10992@yopmail.com</t>
-  </si>
-  <si>
-    <t>gvvtest74040</t>
+    <t>gvvtest71933</t>
+  </si>
+  <si>
+    <t>gvvtest9671@yopmail.com</t>
   </si>
 </sst>
 </file>
@@ -446,7 +440,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:Q3"/>
+  <dimension ref="A1:Q2"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="4.88671875" bestFit="1" customWidth="1"/>
@@ -572,65 +566,10 @@
         <v>9977551133</v>
       </c>
     </row>
-    <row r="3" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
-        <v>3</v>
-      </c>
-      <c r="B3" t="s">
-        <v>5</v>
-      </c>
-      <c r="C3" t="s">
-        <v>30</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="E3" t="s">
-        <v>8</v>
-      </c>
-      <c r="F3" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="G3">
-        <v>23</v>
-      </c>
-      <c r="H3" t="s">
-        <v>14</v>
-      </c>
-      <c r="I3">
-        <v>2000</v>
-      </c>
-      <c r="J3" t="s">
-        <v>6</v>
-      </c>
-      <c r="K3" t="s">
-        <v>6</v>
-      </c>
-      <c r="L3" t="s">
-        <v>23</v>
-      </c>
-      <c r="M3" t="s">
-        <v>24</v>
-      </c>
-      <c r="N3" t="s">
-        <v>26</v>
-      </c>
-      <c r="O3" t="s">
-        <v>25</v>
-      </c>
-      <c r="P3">
-        <v>500335</v>
-      </c>
-      <c r="Q3">
-        <v>9977551133</v>
-      </c>
-    </row>
   </sheetData>
   <hyperlinks>
     <hyperlink ref="D2" r:id="rId1" xr:uid="{D6A3B950-DB4D-483C-A98B-15EE16C9FA39}"/>
     <hyperlink ref="F2" r:id="rId2" xr:uid="{851D07DC-EC92-4332-AB7B-07EC8056F930}"/>
-    <hyperlink ref="D3" r:id="rId3" xr:uid="{4D2B3D44-0F7E-46B5-ACE0-D722AEA02DBB}"/>
-    <hyperlink ref="F3" r:id="rId4" xr:uid="{029352C1-01BF-48E4-9A4A-2400EDF19CB2}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/test-data/testData.xlsx
+++ b/test-data/testData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\WorkSpace\ecommerce_shopfy\test-data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3B713BEE-6275-4D82-83B3-B93ABA4FCDE1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{73212249-CB66-46E1-BC4A-C99DE1E0CD0A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1152" yWindow="1152" windowWidth="17280" windowHeight="8880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="34">
   <si>
     <t>Name</t>
   </si>
@@ -36,89 +36,104 @@
     <t>Case</t>
   </si>
   <si>
+    <t>Run</t>
+  </si>
+  <si>
+    <t>yes</t>
+  </si>
+  <si>
+    <t>Gender</t>
+  </si>
+  <si>
+    <t>male</t>
+  </si>
+  <si>
+    <t>Password</t>
+  </si>
+  <si>
+    <t>Day</t>
+  </si>
+  <si>
+    <t>Month</t>
+  </si>
+  <si>
+    <t>Year</t>
+  </si>
+  <si>
+    <t>FirstName</t>
+  </si>
+  <si>
+    <t>LastName</t>
+  </si>
+  <si>
+    <t>Address</t>
+  </si>
+  <si>
+    <t>Address2</t>
+  </si>
+  <si>
+    <t>State</t>
+  </si>
+  <si>
+    <t>City</t>
+  </si>
+  <si>
+    <t>Zipcode</t>
+  </si>
+  <si>
+    <t>Mobile</t>
+  </si>
+  <si>
+    <t>Invalid</t>
+  </si>
+  <si>
+    <t>gvv1</t>
+  </si>
+  <si>
+    <t>gvv1@yopmail.com</t>
+  </si>
+  <si>
+    <t>July</t>
+  </si>
+  <si>
+    <t>Road no 9</t>
+  </si>
+  <si>
+    <t>Road no 10</t>
+  </si>
+  <si>
     <t>valid</t>
   </si>
   <si>
-    <t>Run</t>
-  </si>
-  <si>
-    <t>yes</t>
-  </si>
-  <si>
-    <t>prasad15</t>
-  </si>
-  <si>
-    <t>Gender</t>
-  </si>
-  <si>
-    <t>male</t>
-  </si>
-  <si>
-    <t>Password</t>
-  </si>
-  <si>
-    <t>Prasad@123</t>
-  </si>
-  <si>
-    <t>Day</t>
-  </si>
-  <si>
-    <t>Month</t>
-  </si>
-  <si>
-    <t>Year</t>
-  </si>
-  <si>
-    <t>September</t>
-  </si>
-  <si>
-    <t>FirstName</t>
-  </si>
-  <si>
-    <t>LastName</t>
-  </si>
-  <si>
-    <t>Address</t>
-  </si>
-  <si>
-    <t>Address2</t>
-  </si>
-  <si>
-    <t>State</t>
-  </si>
-  <si>
-    <t>City</t>
-  </si>
-  <si>
-    <t>Zipcode</t>
-  </si>
-  <si>
-    <t>Mobile</t>
-  </si>
-  <si>
-    <t>Road no 1</t>
-  </si>
-  <si>
-    <t>Road no 2</t>
-  </si>
-  <si>
-    <t>Kakinada</t>
+    <t>female</t>
+  </si>
+  <si>
+    <t>Prasad02</t>
+  </si>
+  <si>
+    <t>gvv</t>
+  </si>
+  <si>
+    <t>prasad</t>
   </si>
   <si>
     <t>Andhra</t>
   </si>
   <si>
-    <t>gvvtest71933</t>
-  </si>
-  <si>
-    <t>gvvtest9671@yopmail.com</t>
+    <t>kakinada</t>
+  </si>
+  <si>
+    <t>gvv3</t>
+  </si>
+  <si>
+    <t>gvv3@yopmail.com</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -130,6 +145,12 @@
       <u/>
       <sz val="11"/>
       <color theme="10"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="8"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -440,24 +461,26 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:Q2"/>
+  <dimension ref="A1:Q3"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="4.88671875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="4.109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="8.44140625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="22.21875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="6.88671875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="6.21875" customWidth="1"/>
+    <col min="2" max="2" width="5.109375" customWidth="1"/>
+    <col min="3" max="3" width="13.44140625" customWidth="1"/>
+    <col min="4" max="4" width="24.5546875" customWidth="1"/>
+    <col min="5" max="5" width="7.21875" customWidth="1"/>
     <col min="6" max="6" width="11.21875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="4.109375" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="9.77734375" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="5" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="9.33203125" bestFit="1" customWidth="1"/>
-    <col min="11" max="13" width="9.21875" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="6.77734375" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="8.33203125" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="7.33203125" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="11" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="4.88671875" customWidth="1"/>
+    <col min="8" max="8" width="10.109375" customWidth="1"/>
+    <col min="9" max="9" width="5.77734375" customWidth="1"/>
+    <col min="10" max="10" width="9.88671875" customWidth="1"/>
+    <col min="11" max="11" width="9.21875" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="9.88671875" customWidth="1"/>
+    <col min="13" max="13" width="10.33203125" customWidth="1"/>
+    <col min="14" max="14" width="7.77734375" customWidth="1"/>
+    <col min="15" max="15" width="9.109375" customWidth="1"/>
+    <col min="16" max="16" width="9.77734375" customWidth="1"/>
+    <col min="17" max="17" width="11.6640625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:17" x14ac:dyDescent="0.3">
@@ -465,7 +488,7 @@
         <v>2</v>
       </c>
       <c r="B1" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C1" t="s">
         <v>0</v>
@@ -474,78 +497,78 @@
         <v>1</v>
       </c>
       <c r="E1" t="s">
+        <v>5</v>
+      </c>
+      <c r="F1" t="s">
         <v>7</v>
       </c>
-      <c r="F1" t="s">
+      <c r="G1" t="s">
+        <v>8</v>
+      </c>
+      <c r="H1" t="s">
         <v>9</v>
       </c>
-      <c r="G1" t="s">
+      <c r="I1" t="s">
+        <v>10</v>
+      </c>
+      <c r="J1" t="s">
         <v>11</v>
       </c>
-      <c r="H1" t="s">
+      <c r="K1" t="s">
         <v>12</v>
       </c>
-      <c r="I1" t="s">
+      <c r="L1" t="s">
         <v>13</v>
       </c>
-      <c r="J1" t="s">
+      <c r="M1" t="s">
+        <v>14</v>
+      </c>
+      <c r="N1" t="s">
         <v>15</v>
       </c>
-      <c r="K1" t="s">
+      <c r="O1" t="s">
         <v>16</v>
       </c>
-      <c r="L1" t="s">
+      <c r="P1" t="s">
         <v>17</v>
       </c>
-      <c r="M1" t="s">
+      <c r="Q1" t="s">
         <v>18</v>
-      </c>
-      <c r="N1" t="s">
-        <v>19</v>
-      </c>
-      <c r="O1" t="s">
-        <v>20</v>
-      </c>
-      <c r="P1" t="s">
-        <v>21</v>
-      </c>
-      <c r="Q1" t="s">
-        <v>22</v>
       </c>
     </row>
     <row r="2" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>3</v>
+        <v>25</v>
       </c>
       <c r="B2" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C2" t="s">
+        <v>32</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="E2" t="s">
+        <v>26</v>
+      </c>
+      <c r="F2" t="s">
         <v>27</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="E2" t="s">
-        <v>8</v>
-      </c>
-      <c r="F2" s="1" t="s">
-        <v>10</v>
       </c>
       <c r="G2">
         <v>23</v>
       </c>
       <c r="H2" t="s">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="I2">
-        <v>2000</v>
+        <v>1990</v>
       </c>
       <c r="J2" t="s">
-        <v>6</v>
+        <v>28</v>
       </c>
       <c r="K2" t="s">
-        <v>6</v>
+        <v>29</v>
       </c>
       <c r="L2" t="s">
         <v>23</v>
@@ -554,22 +577,55 @@
         <v>24</v>
       </c>
       <c r="N2" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="O2" t="s">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="P2">
         <v>500335</v>
       </c>
       <c r="Q2">
-        <v>9977551133</v>
+        <v>9988774455</v>
+      </c>
+    </row>
+    <row r="3" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>19</v>
+      </c>
+      <c r="B3" t="s">
+        <v>4</v>
+      </c>
+      <c r="C3" t="s">
+        <v>20</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="E3" t="s">
+        <v>6</v>
+      </c>
+      <c r="G3">
+        <v>23</v>
+      </c>
+      <c r="H3" t="s">
+        <v>22</v>
+      </c>
+      <c r="I3">
+        <v>1990</v>
+      </c>
+      <c r="L3" t="s">
+        <v>23</v>
+      </c>
+      <c r="M3" t="s">
+        <v>24</v>
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="2" type="noConversion"/>
   <hyperlinks>
-    <hyperlink ref="D2" r:id="rId1" xr:uid="{D6A3B950-DB4D-483C-A98B-15EE16C9FA39}"/>
-    <hyperlink ref="F2" r:id="rId2" xr:uid="{851D07DC-EC92-4332-AB7B-07EC8056F930}"/>
+    <hyperlink ref="D3" r:id="rId1" xr:uid="{09D6043E-1C09-4C93-9C5F-D090433018DF}"/>
+    <hyperlink ref="D2" r:id="rId2" xr:uid="{69C525D9-A1AC-4A99-8E3C-E1F95DCB80C8}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/test-data/testData.xlsx
+++ b/test-data/testData.xlsx
@@ -8,12 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\WorkSpace\ecommerce_shopfy\test-data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{73212249-CB66-46E1-BC4A-C99DE1E0CD0A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4A296FA1-E5B7-45C1-A6BF-4A1E5DBA03C8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="register" sheetId="1" r:id="rId1"/>
+    <sheet name="login" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -25,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="41">
   <si>
     <t>Name</t>
   </si>
@@ -39,9 +40,6 @@
     <t>Run</t>
   </si>
   <si>
-    <t>yes</t>
-  </si>
-  <si>
     <t>Gender</t>
   </si>
   <si>
@@ -84,9 +82,6 @@
     <t>Mobile</t>
   </si>
   <si>
-    <t>Invalid</t>
-  </si>
-  <si>
     <t>gvv1</t>
   </si>
   <si>
@@ -102,9 +97,6 @@
     <t>Road no 10</t>
   </si>
   <si>
-    <t>valid</t>
-  </si>
-  <si>
     <t>female</t>
   </si>
   <si>
@@ -123,10 +115,40 @@
     <t>kakinada</t>
   </si>
   <si>
-    <t>gvv3</t>
-  </si>
-  <si>
-    <t>gvv3@yopmail.com</t>
+    <t>gvv5</t>
+  </si>
+  <si>
+    <t>gvv9</t>
+  </si>
+  <si>
+    <t>gvv9@yopmail.com</t>
+  </si>
+  <si>
+    <t>Negative</t>
+  </si>
+  <si>
+    <t>No</t>
+  </si>
+  <si>
+    <t>Yes</t>
+  </si>
+  <si>
+    <t>Positive</t>
+  </si>
+  <si>
+    <t>gvvtest70902</t>
+  </si>
+  <si>
+    <t>gvvtest70962@yopmail.com</t>
+  </si>
+  <si>
+    <t>Prasad@123</t>
+  </si>
+  <si>
+    <t>gvvtest1@gmail.com</t>
+  </si>
+  <si>
+    <t>gvvtest1</t>
   </si>
 </sst>
 </file>
@@ -461,11 +483,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:Q3"/>
+  <dimension ref="A1:Q4"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="6.21875" customWidth="1"/>
-    <col min="2" max="2" width="5.109375" customWidth="1"/>
+    <col min="2" max="2" width="9.44140625" customWidth="1"/>
     <col min="3" max="3" width="13.44140625" customWidth="1"/>
     <col min="4" max="4" width="24.5546875" customWidth="1"/>
     <col min="5" max="5" width="7.21875" customWidth="1"/>
@@ -485,10 +506,10 @@
   <sheetData>
     <row r="1" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1" t="s">
         <v>2</v>
-      </c>
-      <c r="B1" t="s">
-        <v>3</v>
       </c>
       <c r="C1" t="s">
         <v>0</v>
@@ -497,90 +518,90 @@
         <v>1</v>
       </c>
       <c r="E1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F1" t="s">
+        <v>6</v>
+      </c>
+      <c r="G1" t="s">
         <v>7</v>
       </c>
-      <c r="G1" t="s">
+      <c r="H1" t="s">
         <v>8</v>
       </c>
-      <c r="H1" t="s">
+      <c r="I1" t="s">
         <v>9</v>
       </c>
-      <c r="I1" t="s">
+      <c r="J1" t="s">
         <v>10</v>
       </c>
-      <c r="J1" t="s">
+      <c r="K1" t="s">
         <v>11</v>
       </c>
-      <c r="K1" t="s">
+      <c r="L1" t="s">
         <v>12</v>
       </c>
-      <c r="L1" t="s">
+      <c r="M1" t="s">
         <v>13</v>
       </c>
-      <c r="M1" t="s">
+      <c r="N1" t="s">
         <v>14</v>
       </c>
-      <c r="N1" t="s">
+      <c r="O1" t="s">
         <v>15</v>
       </c>
-      <c r="O1" t="s">
+      <c r="P1" t="s">
         <v>16</v>
       </c>
-      <c r="P1" t="s">
+      <c r="Q1" t="s">
         <v>17</v>
-      </c>
-      <c r="Q1" t="s">
-        <v>18</v>
       </c>
     </row>
     <row r="2" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>25</v>
+        <v>34</v>
       </c>
       <c r="B2" t="s">
-        <v>4</v>
+        <v>32</v>
       </c>
       <c r="C2" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="E2" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="F2" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="G2">
         <v>23</v>
       </c>
       <c r="H2" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="I2">
         <v>1990</v>
       </c>
       <c r="J2" t="s">
+        <v>25</v>
+      </c>
+      <c r="K2" t="s">
+        <v>26</v>
+      </c>
+      <c r="L2" t="s">
+        <v>21</v>
+      </c>
+      <c r="M2" t="s">
+        <v>22</v>
+      </c>
+      <c r="N2" t="s">
+        <v>27</v>
+      </c>
+      <c r="O2" t="s">
         <v>28</v>
-      </c>
-      <c r="K2" t="s">
-        <v>29</v>
-      </c>
-      <c r="L2" t="s">
-        <v>23</v>
-      </c>
-      <c r="M2" t="s">
-        <v>24</v>
-      </c>
-      <c r="N2" t="s">
-        <v>30</v>
-      </c>
-      <c r="O2" t="s">
-        <v>31</v>
       </c>
       <c r="P2">
         <v>500335</v>
@@ -591,41 +612,165 @@
     </row>
     <row r="3" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>19</v>
+        <v>33</v>
       </c>
       <c r="B3" t="s">
-        <v>4</v>
+        <v>32</v>
       </c>
       <c r="C3" t="s">
-        <v>20</v>
+        <v>29</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="E3" t="s">
-        <v>6</v>
+        <v>23</v>
+      </c>
+      <c r="F3" t="s">
+        <v>24</v>
       </c>
       <c r="G3">
         <v>23</v>
       </c>
       <c r="H3" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="I3">
         <v>1990</v>
       </c>
+      <c r="J3" t="s">
+        <v>25</v>
+      </c>
+      <c r="K3" t="s">
+        <v>26</v>
+      </c>
       <c r="L3" t="s">
+        <v>21</v>
+      </c>
+      <c r="M3" t="s">
+        <v>22</v>
+      </c>
+      <c r="N3" t="s">
+        <v>27</v>
+      </c>
+      <c r="O3" t="s">
+        <v>28</v>
+      </c>
+      <c r="P3">
+        <v>500335</v>
+      </c>
+      <c r="Q3">
+        <v>9988774455</v>
+      </c>
+    </row>
+    <row r="4" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>34</v>
+      </c>
+      <c r="B4" t="s">
+        <v>32</v>
+      </c>
+      <c r="C4" t="s">
+        <v>18</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E4" t="s">
+        <v>5</v>
+      </c>
+      <c r="G4">
         <v>23</v>
       </c>
-      <c r="M3" t="s">
-        <v>24</v>
+      <c r="H4" t="s">
+        <v>20</v>
+      </c>
+      <c r="I4">
+        <v>1990</v>
+      </c>
+      <c r="L4" t="s">
+        <v>21</v>
+      </c>
+      <c r="M4" t="s">
+        <v>22</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <hyperlinks>
-    <hyperlink ref="D3" r:id="rId1" xr:uid="{09D6043E-1C09-4C93-9C5F-D090433018DF}"/>
-    <hyperlink ref="D2" r:id="rId2" xr:uid="{69C525D9-A1AC-4A99-8E3C-E1F95DCB80C8}"/>
+    <hyperlink ref="D4" r:id="rId1" xr:uid="{09D6043E-1C09-4C93-9C5F-D090433018DF}"/>
+    <hyperlink ref="D3" r:id="rId2" display="gvv5@yopmail.com" xr:uid="{69C525D9-A1AC-4A99-8E3C-E1F95DCB80C8}"/>
+    <hyperlink ref="D2" r:id="rId3" xr:uid="{87E608F6-2070-4106-B3C4-E355E5CB1189}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{699BB4D7-F512-4D17-8760-A05D5CEF2622}">
+  <dimension ref="A1:E3"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="3" max="3" width="18.21875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="24.44140625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="11.21875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C1" t="s">
+        <v>0</v>
+      </c>
+      <c r="D1" t="s">
+        <v>1</v>
+      </c>
+      <c r="E1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>34</v>
+      </c>
+      <c r="B2" t="s">
+        <v>35</v>
+      </c>
+      <c r="C2" t="s">
+        <v>36</v>
+      </c>
+      <c r="D2" t="s">
+        <v>37</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>34</v>
+      </c>
+      <c r="B3" t="s">
+        <v>32</v>
+      </c>
+      <c r="C3" t="s">
+        <v>40</v>
+      </c>
+      <c r="D3" t="s">
+        <v>39</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>38</v>
+      </c>
+    </row>
+  </sheetData>
+  <hyperlinks>
+    <hyperlink ref="E2" r:id="rId1" xr:uid="{349DE345-6CE0-4273-983F-7B0939AD6FE8}"/>
+    <hyperlink ref="E3" r:id="rId2" xr:uid="{C805C881-BFE0-4725-9B9C-D5D55A530E22}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/test-data/testData.xlsx
+++ b/test-data/testData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\WorkSpace\ecommerce_shopfy\test-data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4A296FA1-E5B7-45C1-A6BF-4A1E5DBA03C8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3E4FB02D-3296-4D41-A087-046F63D1968B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="register" sheetId="1" r:id="rId1"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="39">
   <si>
     <t>Name</t>
   </si>
@@ -115,9 +115,6 @@
     <t>kakinada</t>
   </si>
   <si>
-    <t>gvv5</t>
-  </si>
-  <si>
     <t>gvv9</t>
   </si>
   <si>
@@ -125,9 +122,6 @@
   </si>
   <si>
     <t>Negative</t>
-  </si>
-  <si>
-    <t>No</t>
   </si>
   <si>
     <t>Yes</t>
@@ -483,7 +477,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:Q4"/>
+  <dimension ref="A1:Q3"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="9.44140625" customWidth="1"/>
@@ -559,16 +553,16 @@
     </row>
     <row r="2" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="B2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C2" t="s">
+        <v>29</v>
+      </c>
+      <c r="D2" s="1" t="s">
         <v>30</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>31</v>
       </c>
       <c r="E2" t="s">
         <v>23</v>
@@ -612,22 +606,19 @@
     </row>
     <row r="3" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C3" t="s">
-        <v>29</v>
+        <v>18</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>29</v>
+        <v>19</v>
       </c>
       <c r="E3" t="s">
-        <v>23</v>
-      </c>
-      <c r="F3" t="s">
-        <v>24</v>
+        <v>5</v>
       </c>
       <c r="G3">
         <v>23</v>
@@ -638,69 +629,18 @@
       <c r="I3">
         <v>1990</v>
       </c>
-      <c r="J3" t="s">
-        <v>25</v>
-      </c>
-      <c r="K3" t="s">
-        <v>26</v>
-      </c>
       <c r="L3" t="s">
         <v>21</v>
       </c>
       <c r="M3" t="s">
-        <v>22</v>
-      </c>
-      <c r="N3" t="s">
-        <v>27</v>
-      </c>
-      <c r="O3" t="s">
-        <v>28</v>
-      </c>
-      <c r="P3">
-        <v>500335</v>
-      </c>
-      <c r="Q3">
-        <v>9988774455</v>
-      </c>
-    </row>
-    <row r="4" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
-        <v>34</v>
-      </c>
-      <c r="B4" t="s">
-        <v>32</v>
-      </c>
-      <c r="C4" t="s">
-        <v>18</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="E4" t="s">
-        <v>5</v>
-      </c>
-      <c r="G4">
-        <v>23</v>
-      </c>
-      <c r="H4" t="s">
-        <v>20</v>
-      </c>
-      <c r="I4">
-        <v>1990</v>
-      </c>
-      <c r="L4" t="s">
-        <v>21</v>
-      </c>
-      <c r="M4" t="s">
         <v>22</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <hyperlinks>
-    <hyperlink ref="D4" r:id="rId1" xr:uid="{09D6043E-1C09-4C93-9C5F-D090433018DF}"/>
-    <hyperlink ref="D3" r:id="rId2" display="gvv5@yopmail.com" xr:uid="{69C525D9-A1AC-4A99-8E3C-E1F95DCB80C8}"/>
-    <hyperlink ref="D2" r:id="rId3" xr:uid="{87E608F6-2070-4106-B3C4-E355E5CB1189}"/>
+    <hyperlink ref="D3" r:id="rId1" xr:uid="{09D6043E-1C09-4C93-9C5F-D090433018DF}"/>
+    <hyperlink ref="D2" r:id="rId2" xr:uid="{87E608F6-2070-4106-B3C4-E355E5CB1189}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -735,36 +675,36 @@
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
+        <v>32</v>
+      </c>
+      <c r="B2" t="s">
+        <v>33</v>
+      </c>
+      <c r="C2" t="s">
         <v>34</v>
       </c>
-      <c r="B2" t="s">
+      <c r="D2" t="s">
         <v>35</v>
       </c>
-      <c r="C2" t="s">
+      <c r="E2" s="1" t="s">
         <v>36</v>
-      </c>
-      <c r="D2" t="s">
-        <v>37</v>
-      </c>
-      <c r="E2" s="1" t="s">
-        <v>38</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="B3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C3" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="D3" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
     </row>
   </sheetData>

--- a/test-data/testData.xlsx
+++ b/test-data/testData.xlsx
@@ -1,20 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29929"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\WorkSpace\ecommerce_shopfy\test-data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3E4FB02D-3296-4D41-A087-046F63D1968B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8ECD7177-B1DE-48A1-99CA-E6932BDA84E1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="register" sheetId="1" r:id="rId1"/>
     <sheet name="login" sheetId="2" r:id="rId2"/>
+    <sheet name="Sheet1" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -26,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="40">
   <si>
     <t>Name</t>
   </si>
@@ -143,6 +144,9 @@
   </si>
   <si>
     <t>gvvtest1</t>
+  </si>
+  <si>
+    <t>Quantity</t>
   </si>
 </sst>
 </file>
@@ -714,4 +718,28 @@
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CE99E6B8-824C-4732-B2C5-23DC1F2D6217}">
+  <dimension ref="A1:D1"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetData>
+    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C1" t="s">
+        <v>0</v>
+      </c>
+      <c r="D1" t="s">
+        <v>39</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/test-data/testData.xlsx
+++ b/test-data/testData.xlsx
@@ -8,14 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\WorkSpace\ecommerce_shopfy\test-data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8ECD7177-B1DE-48A1-99CA-E6932BDA84E1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CF8778F3-EE48-4FF9-9D60-BD8E6B5DD7A7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="register" sheetId="1" r:id="rId1"/>
     <sheet name="login" sheetId="2" r:id="rId2"/>
-    <sheet name="Sheet1" sheetId="3" r:id="rId3"/>
+    <sheet name="products" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="44">
   <si>
     <t>Name</t>
   </si>
@@ -147,6 +147,18 @@
   </si>
   <si>
     <t>Quantity</t>
+  </si>
+  <si>
+    <t>Men Tshirt</t>
+  </si>
+  <si>
+    <t>Sleeveless Dress</t>
+  </si>
+  <si>
+    <t>Stylish Dress</t>
+  </si>
+  <si>
+    <t>Premium Polo T-Shirts</t>
   </si>
 </sst>
 </file>
@@ -722,8 +734,11 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CE99E6B8-824C-4732-B2C5-23DC1F2D6217}">
-  <dimension ref="A1:D1"/>
+  <dimension ref="A1:D5"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="3" max="3" width="19.109375" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
@@ -739,6 +754,62 @@
         <v>39</v>
       </c>
     </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>32</v>
+      </c>
+      <c r="B2" t="s">
+        <v>33</v>
+      </c>
+      <c r="C2" t="s">
+        <v>40</v>
+      </c>
+      <c r="D2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>32</v>
+      </c>
+      <c r="B3" t="s">
+        <v>33</v>
+      </c>
+      <c r="C3" t="s">
+        <v>41</v>
+      </c>
+      <c r="D3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>32</v>
+      </c>
+      <c r="B4" t="s">
+        <v>33</v>
+      </c>
+      <c r="C4" t="s">
+        <v>42</v>
+      </c>
+      <c r="D4">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>32</v>
+      </c>
+      <c r="B5" t="s">
+        <v>33</v>
+      </c>
+      <c r="C5" t="s">
+        <v>43</v>
+      </c>
+      <c r="D5">
+        <v>4</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/test-data/testData.xlsx
+++ b/test-data/testData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\WorkSpace\ecommerce_shopfy\test-data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CF8778F3-EE48-4FF9-9D60-BD8E6B5DD7A7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CF69815E-A0FE-4E2B-BB0B-4FB9B0C7D909}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="21840" windowHeight="13020" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="register" sheetId="1" r:id="rId1"/>
@@ -140,25 +140,25 @@
     <t>Prasad@123</t>
   </si>
   <si>
+    <t>Quantity</t>
+  </si>
+  <si>
+    <t>Men Tshirt</t>
+  </si>
+  <si>
+    <t>Sleeveless Dress</t>
+  </si>
+  <si>
+    <t>Stylish Dress</t>
+  </si>
+  <si>
+    <t>Premium Polo T-Shirts</t>
+  </si>
+  <si>
+    <t>gvvtest1</t>
+  </si>
+  <si>
     <t>gvvtest1@gmail.com</t>
-  </si>
-  <si>
-    <t>gvvtest1</t>
-  </si>
-  <si>
-    <t>Quantity</t>
-  </si>
-  <si>
-    <t>Men Tshirt</t>
-  </si>
-  <si>
-    <t>Sleeveless Dress</t>
-  </si>
-  <si>
-    <t>Stylish Dress</t>
-  </si>
-  <si>
-    <t>Premium Polo T-Shirts</t>
   </si>
 </sst>
 </file>
@@ -714,10 +714,10 @@
         <v>31</v>
       </c>
       <c r="C3" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="D3" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="E3" s="1" t="s">
         <v>36</v>
@@ -726,7 +726,6 @@
   </sheetData>
   <hyperlinks>
     <hyperlink ref="E2" r:id="rId1" xr:uid="{349DE345-6CE0-4273-983F-7B0939AD6FE8}"/>
-    <hyperlink ref="E3" r:id="rId2" xr:uid="{C805C881-BFE0-4725-9B9C-D5D55A530E22}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -751,7 +750,7 @@
         <v>0</v>
       </c>
       <c r="D1" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.3">
@@ -762,7 +761,7 @@
         <v>33</v>
       </c>
       <c r="C2" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="D2">
         <v>2</v>
@@ -776,7 +775,7 @@
         <v>33</v>
       </c>
       <c r="C3" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="D3">
         <v>1</v>
@@ -790,7 +789,7 @@
         <v>33</v>
       </c>
       <c r="C4" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="D4">
         <v>3</v>
@@ -804,7 +803,7 @@
         <v>33</v>
       </c>
       <c r="C5" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="D5">
         <v>4</v>

--- a/test-data/testData.xlsx
+++ b/test-data/testData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\WorkSpace\ecommerce_shopfy\test-data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8ECD7177-B1DE-48A1-99CA-E6932BDA84E1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CD160EE6-1C6C-419C-ACA0-0B1817D81A15}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="register" sheetId="1" r:id="rId1"/>
@@ -481,7 +481,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:Q3"/>
+  <dimension ref="A1:Q4"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="9.44140625" customWidth="1"/>
@@ -639,6 +639,9 @@
       <c r="M3" t="s">
         <v>22</v>
       </c>
+    </row>
+    <row r="4" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="D4" s="1"/>
     </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
